--- a/artfynd/A 49560-2025 artfynd.xlsx
+++ b/artfynd/A 49560-2025 artfynd.xlsx
@@ -1421,42 +1421,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129541131</v>
+        <v>129541462</v>
       </c>
       <c r="B9" t="n">
-        <v>57724</v>
+        <v>92832</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1464,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583300</v>
+        <v>583244</v>
       </c>
       <c r="R9" t="n">
-        <v>6400540</v>
+        <v>6400522</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,17 +1505,13 @@
           <t>2025-11-05</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Bearbetat död stam</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1531,45 +1530,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129541462</v>
+        <v>129541131</v>
       </c>
       <c r="B10" t="n">
-        <v>92832</v>
+        <v>57724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1577,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583244</v>
+        <v>583300</v>
       </c>
       <c r="R10" t="n">
-        <v>6400522</v>
+        <v>6400540</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,13 +1611,17 @@
           <t>2025-11-05</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Bearbetat död stam</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49560-2025 artfynd.xlsx
+++ b/artfynd/A 49560-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129541496</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129541404</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129541370</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129541431</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>129541348</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>129541218</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>129541395</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>129541462</v>
       </c>
       <c r="B9" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 49560-2025 artfynd.xlsx
+++ b/artfynd/A 49560-2025 artfynd.xlsx
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129541348</v>
+        <v>129541218</v>
       </c>
       <c r="B6" t="n">
         <v>98727</v>
@@ -1127,7 +1127,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1142,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583199</v>
+        <v>583278</v>
       </c>
       <c r="R6" t="n">
-        <v>6400575</v>
+        <v>6400561</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1209,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129541218</v>
+        <v>129541348</v>
       </c>
       <c r="B7" t="n">
         <v>98727</v>
@@ -1233,11 +1237,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583278</v>
+        <v>583199</v>
       </c>
       <c r="R7" t="n">
-        <v>6400561</v>
+        <v>6400575</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 49560-2025 artfynd.xlsx
+++ b/artfynd/A 49560-2025 artfynd.xlsx
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129541218</v>
+        <v>129541348</v>
       </c>
       <c r="B6" t="n">
         <v>98727</v>
@@ -1127,11 +1127,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1146,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583278</v>
+        <v>583199</v>
       </c>
       <c r="R6" t="n">
-        <v>6400561</v>
+        <v>6400575</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129541348</v>
+        <v>129541218</v>
       </c>
       <c r="B7" t="n">
         <v>98727</v>
@@ -1237,7 +1233,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583199</v>
+        <v>583278</v>
       </c>
       <c r="R7" t="n">
-        <v>6400575</v>
+        <v>6400561</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 49560-2025 artfynd.xlsx
+++ b/artfynd/A 49560-2025 artfynd.xlsx
@@ -1421,45 +1421,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129541462</v>
+        <v>129541131</v>
       </c>
       <c r="B9" t="n">
-        <v>92835</v>
+        <v>57724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1467,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583244</v>
+        <v>583300</v>
       </c>
       <c r="R9" t="n">
-        <v>6400522</v>
+        <v>6400540</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,13 +1502,17 @@
           <t>2025-11-05</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Bearbetat död stam</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1530,42 +1531,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129541131</v>
+        <v>129541462</v>
       </c>
       <c r="B10" t="n">
-        <v>57724</v>
+        <v>92835</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1573,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583300</v>
+        <v>583244</v>
       </c>
       <c r="R10" t="n">
-        <v>6400540</v>
+        <v>6400522</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,17 +1615,13 @@
           <t>2025-11-05</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Bearbetat död stam</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49560-2025 artfynd.xlsx
+++ b/artfynd/A 49560-2025 artfynd.xlsx
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129541348</v>
+        <v>129541218</v>
       </c>
       <c r="B6" t="n">
         <v>98727</v>
@@ -1127,7 +1127,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1142,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583199</v>
+        <v>583278</v>
       </c>
       <c r="R6" t="n">
-        <v>6400575</v>
+        <v>6400561</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1209,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129541218</v>
+        <v>129541348</v>
       </c>
       <c r="B7" t="n">
         <v>98727</v>
@@ -1233,11 +1237,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583278</v>
+        <v>583199</v>
       </c>
       <c r="R7" t="n">
-        <v>6400561</v>
+        <v>6400575</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1421,42 +1421,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129541131</v>
+        <v>129541462</v>
       </c>
       <c r="B9" t="n">
-        <v>57724</v>
+        <v>92835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1464,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583300</v>
+        <v>583244</v>
       </c>
       <c r="R9" t="n">
-        <v>6400540</v>
+        <v>6400522</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,17 +1505,13 @@
           <t>2025-11-05</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Bearbetat död stam</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1531,45 +1530,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129541462</v>
+        <v>129541131</v>
       </c>
       <c r="B10" t="n">
-        <v>92835</v>
+        <v>57724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1577,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583244</v>
+        <v>583300</v>
       </c>
       <c r="R10" t="n">
-        <v>6400522</v>
+        <v>6400540</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,13 +1611,17 @@
           <t>2025-11-05</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Bearbetat död stam</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49560-2025 artfynd.xlsx
+++ b/artfynd/A 49560-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129541496</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129541404</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129541370</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129541431</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>129541348</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>129541218</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>129541395</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,45 +1421,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129541462</v>
+        <v>129541131</v>
       </c>
       <c r="B9" t="n">
-        <v>92835</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1467,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583244</v>
+        <v>583300</v>
       </c>
       <c r="R9" t="n">
-        <v>6400522</v>
+        <v>6400540</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,13 +1502,17 @@
           <t>2025-11-05</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Bearbetat död stam</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1530,42 +1531,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129541131</v>
+        <v>129541462</v>
       </c>
       <c r="B10" t="n">
-        <v>57724</v>
+        <v>92863</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1573,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583300</v>
+        <v>583244</v>
       </c>
       <c r="R10" t="n">
-        <v>6400540</v>
+        <v>6400522</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,17 +1615,13 @@
           <t>2025-11-05</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Bearbetat död stam</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49560-2025 artfynd.xlsx
+++ b/artfynd/A 49560-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129541496</v>
       </c>
       <c r="B2" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129541404</v>
+        <v>129541370</v>
       </c>
       <c r="B3" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583210</v>
+        <v>583203</v>
       </c>
       <c r="R3" t="n">
-        <v>6400577</v>
+        <v>6400569</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129541370</v>
+        <v>129541404</v>
       </c>
       <c r="B4" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583203</v>
+        <v>583210</v>
       </c>
       <c r="R4" t="n">
-        <v>6400569</v>
+        <v>6400577</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
         <v>129541431</v>
       </c>
       <c r="B5" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129541348</v>
+        <v>129541218</v>
       </c>
       <c r="B6" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,7 +1127,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1142,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583199</v>
+        <v>583278</v>
       </c>
       <c r="R6" t="n">
-        <v>6400575</v>
+        <v>6400561</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129541218</v>
+        <v>129541348</v>
       </c>
       <c r="B7" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1233,11 +1237,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583278</v>
+        <v>583199</v>
       </c>
       <c r="R7" t="n">
-        <v>6400561</v>
+        <v>6400575</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
         <v>129541395</v>
       </c>
       <c r="B8" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,42 +1421,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129541131</v>
+        <v>129541462</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1464,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583300</v>
+        <v>583244</v>
       </c>
       <c r="R9" t="n">
-        <v>6400540</v>
+        <v>6400522</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,17 +1505,13 @@
           <t>2025-11-05</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Bearbetat död stam</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1531,45 +1530,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129541462</v>
+        <v>129541131</v>
       </c>
       <c r="B10" t="n">
-        <v>92863</v>
+        <v>57732</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1577,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583244</v>
+        <v>583300</v>
       </c>
       <c r="R10" t="n">
-        <v>6400522</v>
+        <v>6400540</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,13 +1611,17 @@
           <t>2025-11-05</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Bearbetat död stam</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49560-2025 artfynd.xlsx
+++ b/artfynd/A 49560-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129541496</v>
       </c>
       <c r="B2" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129541370</v>
+        <v>129541404</v>
       </c>
       <c r="B3" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583203</v>
+        <v>583210</v>
       </c>
       <c r="R3" t="n">
-        <v>6400569</v>
+        <v>6400577</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129541404</v>
+        <v>129541370</v>
       </c>
       <c r="B4" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583210</v>
+        <v>583203</v>
       </c>
       <c r="R4" t="n">
-        <v>6400577</v>
+        <v>6400569</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
         <v>129541431</v>
       </c>
       <c r="B5" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129541218</v>
+        <v>129541348</v>
       </c>
       <c r="B6" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,11 +1127,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1146,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583278</v>
+        <v>583199</v>
       </c>
       <c r="R6" t="n">
-        <v>6400561</v>
+        <v>6400575</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129541348</v>
+        <v>129541218</v>
       </c>
       <c r="B7" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1237,7 +1233,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583199</v>
+        <v>583278</v>
       </c>
       <c r="R7" t="n">
-        <v>6400575</v>
+        <v>6400561</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
         <v>129541395</v>
       </c>
       <c r="B8" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,45 +1421,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129541462</v>
+        <v>129541131</v>
       </c>
       <c r="B9" t="n">
-        <v>92869</v>
+        <v>57733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1467,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583244</v>
+        <v>583300</v>
       </c>
       <c r="R9" t="n">
-        <v>6400522</v>
+        <v>6400540</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,13 +1502,17 @@
           <t>2025-11-05</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Bearbetat död stam</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1530,42 +1531,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129541131</v>
+        <v>129541462</v>
       </c>
       <c r="B10" t="n">
-        <v>57732</v>
+        <v>92870</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1573,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583300</v>
+        <v>583244</v>
       </c>
       <c r="R10" t="n">
-        <v>6400540</v>
+        <v>6400522</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,17 +1615,13 @@
           <t>2025-11-05</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Bearbetat död stam</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49560-2025 artfynd.xlsx
+++ b/artfynd/A 49560-2025 artfynd.xlsx
@@ -1421,42 +1421,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129541131</v>
+        <v>129541462</v>
       </c>
       <c r="B9" t="n">
-        <v>57733</v>
+        <v>92870</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1464,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583300</v>
+        <v>583244</v>
       </c>
       <c r="R9" t="n">
-        <v>6400540</v>
+        <v>6400522</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,17 +1505,13 @@
           <t>2025-11-05</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Bearbetat död stam</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1531,45 +1530,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129541462</v>
+        <v>129541131</v>
       </c>
       <c r="B10" t="n">
-        <v>92870</v>
+        <v>57733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1577,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583244</v>
+        <v>583300</v>
       </c>
       <c r="R10" t="n">
-        <v>6400522</v>
+        <v>6400540</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,13 +1611,17 @@
           <t>2025-11-05</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Bearbetat död stam</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49560-2025 artfynd.xlsx
+++ b/artfynd/A 49560-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129541496</v>
       </c>
       <c r="B2" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129541404</v>
       </c>
       <c r="B3" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129541370</v>
       </c>
       <c r="B4" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129541431</v>
       </c>
       <c r="B5" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>129541348</v>
       </c>
       <c r="B6" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>129541218</v>
       </c>
       <c r="B7" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>129541395</v>
       </c>
       <c r="B8" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>129541462</v>
       </c>
       <c r="B9" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 49560-2025 artfynd.xlsx
+++ b/artfynd/A 49560-2025 artfynd.xlsx
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129541404</v>
+        <v>129541370</v>
       </c>
       <c r="B3" t="n">
         <v>98774</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583210</v>
+        <v>583203</v>
       </c>
       <c r="R3" t="n">
-        <v>6400577</v>
+        <v>6400569</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129541370</v>
+        <v>129541404</v>
       </c>
       <c r="B4" t="n">
         <v>98774</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583203</v>
+        <v>583210</v>
       </c>
       <c r="R4" t="n">
-        <v>6400569</v>
+        <v>6400577</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 49560-2025 artfynd.xlsx
+++ b/artfynd/A 49560-2025 artfynd.xlsx
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129541370</v>
+        <v>129541404</v>
       </c>
       <c r="B3" t="n">
         <v>98774</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583203</v>
+        <v>583210</v>
       </c>
       <c r="R3" t="n">
-        <v>6400569</v>
+        <v>6400577</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129541404</v>
+        <v>129541370</v>
       </c>
       <c r="B4" t="n">
         <v>98774</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583210</v>
+        <v>583203</v>
       </c>
       <c r="R4" t="n">
-        <v>6400577</v>
+        <v>6400569</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 49560-2025 artfynd.xlsx
+++ b/artfynd/A 49560-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129541496</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129541404</v>
       </c>
       <c r="B3" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129541370</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129541431</v>
       </c>
       <c r="B5" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>129541348</v>
       </c>
       <c r="B6" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>129541218</v>
       </c>
       <c r="B7" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>129541395</v>
       </c>
       <c r="B8" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>129541462</v>
       </c>
       <c r="B9" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 49560-2025 artfynd.xlsx
+++ b/artfynd/A 49560-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129541496</v>
       </c>
       <c r="B2" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129541404</v>
       </c>
       <c r="B3" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129541370</v>
       </c>
       <c r="B4" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129541431</v>
       </c>
       <c r="B5" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129541348</v>
+        <v>129541218</v>
       </c>
       <c r="B6" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,7 +1127,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1142,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583199</v>
+        <v>583278</v>
       </c>
       <c r="R6" t="n">
-        <v>6400575</v>
+        <v>6400561</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129541218</v>
+        <v>129541348</v>
       </c>
       <c r="B7" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1233,11 +1237,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583278</v>
+        <v>583199</v>
       </c>
       <c r="R7" t="n">
-        <v>6400561</v>
+        <v>6400575</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
         <v>129541395</v>
       </c>
       <c r="B8" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>129541462</v>
       </c>
       <c r="B9" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 49560-2025 artfynd.xlsx
+++ b/artfynd/A 49560-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129541496</v>
       </c>
       <c r="B2" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129541404</v>
       </c>
       <c r="B3" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129541370</v>
       </c>
       <c r="B4" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129541431</v>
       </c>
       <c r="B5" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129541218</v>
+        <v>129541348</v>
       </c>
       <c r="B6" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,11 +1127,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1146,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583278</v>
+        <v>583199</v>
       </c>
       <c r="R6" t="n">
-        <v>6400561</v>
+        <v>6400575</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129541348</v>
+        <v>129541218</v>
       </c>
       <c r="B7" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1237,7 +1233,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583199</v>
+        <v>583278</v>
       </c>
       <c r="R7" t="n">
-        <v>6400575</v>
+        <v>6400561</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
         <v>129541395</v>
       </c>
       <c r="B8" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49560-2025 artfynd.xlsx
+++ b/artfynd/A 49560-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129541496</v>
       </c>
       <c r="B2" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129541404</v>
       </c>
       <c r="B3" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129541370</v>
       </c>
       <c r="B4" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129541431</v>
       </c>
       <c r="B5" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>129541348</v>
       </c>
       <c r="B6" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>129541218</v>
       </c>
       <c r="B7" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>129541395</v>
       </c>
       <c r="B8" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>129541462</v>
       </c>
       <c r="B9" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>129541131</v>
       </c>
       <c r="B10" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
